--- a/sprite_sheet.xlsx
+++ b/sprite_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nthnl\Desktop\Code\Flashtrek-2.0-Godot-4.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05146CBA-BE6C-496D-BA57-70669290DF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBBE4B2-297B-4B3C-A695-40A7122CBBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9480D77A-E5C1-4096-97D1-11AE8DADC1A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9480D77A-E5C1-4096-97D1-11AE8DADC1A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprites" sheetId="1" r:id="rId1"/>
@@ -419,16 +419,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>75520</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>200704</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>7485</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>37418</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>545645</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>477610</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>36737</xdr:rowOff>
+      <xdr:rowOff>172808</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -457,7 +457,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14730413" y="200704"/>
+          <a:off x="15274699" y="336775"/>
           <a:ext cx="11491911" cy="21090390"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/sprite_sheet.xlsx
+++ b/sprite_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nthnl\Desktop\Code\Flashtrek-2.0-Godot-4.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBBE4B2-297B-4B3C-A695-40A7122CBBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E779C4-C3F1-4AB2-B20D-0159C6F61777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9480D77A-E5C1-4096-97D1-11AE8DADC1A6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9480D77A-E5C1-4096-97D1-11AE8DADC1A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprites" sheetId="1" r:id="rId1"/>

--- a/sprite_sheet.xlsx
+++ b/sprite_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nthnl\Desktop\Code\Flashtrek-2.0-Godot-4.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E779C4-C3F1-4AB2-B20D-0159C6F61777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307699B1-BD73-4125-A6C9-E36659E5DDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9480D77A-E5C1-4096-97D1-11AE8DADC1A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Merchantman</t>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -787,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A46386-5A4D-4B73-8EAB-C9B2C9DD0814}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1180,11 +1177,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
